--- a/waardelijst/3.0.0/IMKL-Waardelijsten-changelog-3.0.1.xlsx
+++ b/waardelijst/3.0.0/IMKL-Waardelijsten-changelog-3.0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p.janssen.GNM\Documents\Github\imkl-werkomgeving\4-waardelijsten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p.janssen.GNM\Documents\Github\imkl-werkomgeving\4-waardelijsten\gepubliceerd\op register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB706FD-99D7-4513-9C0D-9703BA8A6B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F670FDB4-59FD-494F-9A2B-7776295C1AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-8010" windowWidth="29040" windowHeight="15720" xr2:uid="{894B1FF5-8DFC-4651-A7C4-67B2EE5B0E46}"/>
+    <workbookView xWindow="33060" yWindow="-3270" windowWidth="29010" windowHeight="17550" xr2:uid="{894B1FF5-8DFC-4651-A7C4-67B2EE5B0E46}"/>
   </bookViews>
   <sheets>
     <sheet name="Changelog" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>Datum</t>
   </si>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>nav externe consultatie</t>
+  </si>
+  <si>
+    <t>2 ontberekende waarden bij graafmethodeValue toegevoegd</t>
+  </si>
+  <si>
+    <t>alleen in skos bestand waardelijsten_imkl_3.0.1.ttl. De waarden stonden wel al in excel.</t>
   </si>
 </sst>
 </file>
@@ -826,12 +832,22 @@
       </c>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5"/>
+    <row r="14" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>20250925</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5">
+        <v>376</v>
+      </c>
       <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2291,18 +2307,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2509,18 +2525,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7893A73B-81F0-482A-B793-D93E5F8DCA71}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB1489CD-B12A-4704-A7E2-006D773FFFBF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB1489CD-B12A-4704-A7E2-006D773FFFBF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7893A73B-81F0-482A-B793-D93E5F8DCA71}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
